--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>92.92802776399527</v>
+        <v>15.10080451164923</v>
       </c>
       <c r="D2" t="n">
-        <v>82.7030400862397</v>
+        <v>13.43924401401395</v>
       </c>
       <c r="E2" t="n">
-        <v>24.48077103483496</v>
+        <v>3.97812529316068</v>
       </c>
       <c r="F2" t="n">
-        <v>21.3724262222936</v>
+        <v>3.473019261122711</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.76104949666017</v>
+        <v>4.023670543207277</v>
       </c>
       <c r="D3" t="n">
-        <v>42.03529528125996</v>
+        <v>6.830735483204744</v>
       </c>
       <c r="E3" t="n">
-        <v>24.48077103483496</v>
+        <v>3.97812529316068</v>
       </c>
       <c r="F3" t="n">
-        <v>21.3724262222936</v>
+        <v>3.473019261122711</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>65.40863396171378</v>
+        <v>10.62890301877849</v>
       </c>
       <c r="D4" t="n">
-        <v>49.20676582004893</v>
+        <v>7.996099445757952</v>
       </c>
       <c r="E4" t="n">
-        <v>24.48077103483496</v>
+        <v>3.97812529316068</v>
       </c>
       <c r="F4" t="n">
-        <v>21.3724262222936</v>
+        <v>3.473019261122711</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.13131801439361</v>
+        <v>8.146339177338961</v>
       </c>
       <c r="D5" t="n">
-        <v>38.20550344946602</v>
+        <v>6.208394310538229</v>
       </c>
       <c r="E5" t="n">
-        <v>24.48077103483496</v>
+        <v>3.97812529316068</v>
       </c>
       <c r="F5" t="n">
-        <v>21.3724262222936</v>
+        <v>3.473019261122711</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>66.40134677170384</v>
+        <v>10.79021885040187</v>
       </c>
       <c r="D6" t="n">
-        <v>57.72312921576793</v>
+        <v>9.380008497562288</v>
       </c>
       <c r="E6" t="n">
-        <v>24.48077103483496</v>
+        <v>3.97812529316068</v>
       </c>
       <c r="F6" t="n">
-        <v>21.3724262222936</v>
+        <v>3.473019261122711</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.22077465432017</v>
+        <v>3.773375881327028</v>
       </c>
       <c r="D7" t="n">
-        <v>15.89060990926734</v>
+        <v>2.582224110255943</v>
       </c>
       <c r="E7" t="n">
-        <v>24.48077103483496</v>
+        <v>3.97812529316068</v>
       </c>
       <c r="F7" t="n">
-        <v>21.3724262222936</v>
+        <v>3.473019261122711</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.56755939732729</v>
+        <v>4.642228402065685</v>
       </c>
       <c r="D8" t="n">
-        <v>21.00430074396778</v>
+        <v>3.413198870894765</v>
       </c>
       <c r="E8" t="n">
-        <v>24.48077103483496</v>
+        <v>3.97812529316068</v>
       </c>
       <c r="F8" t="n">
-        <v>21.3724262222936</v>
+        <v>3.473019261122711</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.32711400041228</v>
+        <v>3.790656025066995</v>
       </c>
       <c r="D9" t="n">
-        <v>17.9734180702462</v>
+        <v>2.920680436415008</v>
       </c>
       <c r="E9" t="n">
-        <v>24.48077103483496</v>
+        <v>3.97812529316068</v>
       </c>
       <c r="F9" t="n">
-        <v>21.3724262222936</v>
+        <v>3.473019261122711</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
